--- a/research/traditional_assets/database/data/singapore/singapore_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_insurance_life.xlsx
@@ -588,40 +588,40 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.03516090584028606</v>
+        <v>0.1850373264626216</v>
       </c>
       <c r="H2">
-        <v>0.03516090584028606</v>
+        <v>0.1850373264626216</v>
       </c>
       <c r="I2">
-        <v>0.07272262898007832</v>
+        <v>0.1246260275394735</v>
       </c>
       <c r="J2">
-        <v>0.05882624435812877</v>
+        <v>0.06231301376973677</v>
       </c>
       <c r="K2">
-        <v>965.9</v>
+        <v>680</v>
       </c>
       <c r="L2">
-        <v>0.05482149951756626</v>
+        <v>0.06417697745311778</v>
       </c>
       <c r="M2">
-        <v>211.2</v>
+        <v>221.1</v>
       </c>
       <c r="N2">
-        <v>0.0298545439124719</v>
+        <v>0.03385703785373025</v>
       </c>
       <c r="O2">
-        <v>0.2186561755875349</v>
+        <v>0.3251470588235294</v>
       </c>
       <c r="P2">
-        <v>211.2</v>
+        <v>221.1</v>
       </c>
       <c r="Q2">
-        <v>0.0298545439124719</v>
+        <v>0.03385703785373025</v>
       </c>
       <c r="R2">
-        <v>0.2186561755875349</v>
+        <v>0.3251470588235294</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,73 +630,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9438</v>
+        <v>10706.5</v>
       </c>
       <c r="V2">
-        <v>1.334124931088588</v>
+        <v>1.639486095798113</v>
       </c>
       <c r="W2">
-        <v>0.1578835529111772</v>
+        <v>0.09430952942318627</v>
       </c>
       <c r="X2">
-        <v>0.05501626696389192</v>
+        <v>0.08660060660469299</v>
       </c>
       <c r="Y2">
-        <v>0.1028672859472853</v>
-      </c>
-      <c r="Z2">
-        <v>14.19856555725683</v>
-      </c>
-      <c r="AA2">
-        <v>0.8352482870061013</v>
+        <v>0.00770892281849328</v>
       </c>
       <c r="AB2">
-        <v>0.0549844564107971</v>
-      </c>
-      <c r="AC2">
-        <v>0.7802638305953042</v>
+        <v>0.08620308001750566</v>
       </c>
       <c r="AD2">
-        <v>6.32</v>
+        <v>55.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.32</v>
+        <v>55.3</v>
       </c>
       <c r="AG2">
-        <v>-9431.68</v>
+        <v>-10651.2</v>
       </c>
       <c r="AH2">
-        <v>0.0008925772036912022</v>
+        <v>0.008396981338354313</v>
       </c>
       <c r="AI2">
-        <v>0.0008669386366566896</v>
+        <v>0.008032653535529602</v>
       </c>
       <c r="AJ2">
-        <v>4.000916271453902</v>
+        <v>2.584740827023878</v>
       </c>
       <c r="AK2">
-        <v>4.390953360832037</v>
+        <v>2.786740273671542</v>
       </c>
       <c r="AL2">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.004749736960769579</v>
-      </c>
-      <c r="AO2">
-        <v>185.4269175108538</v>
+        <v>0.04115195713647864</v>
       </c>
       <c r="AP2">
-        <v>-7.088290996542914</v>
-      </c>
-      <c r="AQ2">
-        <v>185.4269175108538</v>
+        <v>-7.926179490995684</v>
       </c>
     </row>
     <row r="3">
@@ -716,40 +701,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.03516090584028606</v>
+        <v>0.1850373264626216</v>
       </c>
       <c r="H3">
-        <v>0.03516090584028606</v>
+        <v>0.1850373264626216</v>
       </c>
       <c r="I3">
-        <v>0.07272262898007832</v>
+        <v>0.1246260275394735</v>
       </c>
       <c r="J3">
-        <v>0.05882624435812877</v>
+        <v>0.06231301376973677</v>
       </c>
       <c r="K3">
-        <v>965.9</v>
+        <v>680</v>
       </c>
       <c r="L3">
-        <v>0.05482149951756626</v>
+        <v>0.06417697745311778</v>
       </c>
       <c r="M3">
-        <v>211.2</v>
+        <v>221.1</v>
       </c>
       <c r="N3">
-        <v>0.0298545439124719</v>
+        <v>0.03385703785373025</v>
       </c>
       <c r="O3">
-        <v>0.2186561755875349</v>
+        <v>0.3251470588235294</v>
       </c>
       <c r="P3">
-        <v>211.2</v>
+        <v>221.1</v>
       </c>
       <c r="Q3">
-        <v>0.0298545439124719</v>
+        <v>0.03385703785373025</v>
       </c>
       <c r="R3">
-        <v>0.2186561755875349</v>
+        <v>0.3251470588235294</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,73 +743,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9438</v>
+        <v>10706.5</v>
       </c>
       <c r="V3">
-        <v>1.334124931088588</v>
+        <v>1.639486095798113</v>
       </c>
       <c r="W3">
-        <v>0.1578835529111772</v>
+        <v>0.09430952942318627</v>
       </c>
       <c r="X3">
-        <v>0.05501626696389192</v>
+        <v>0.08660060660469299</v>
       </c>
       <c r="Y3">
-        <v>0.1028672859472853</v>
-      </c>
-      <c r="Z3">
-        <v>14.19856555725683</v>
-      </c>
-      <c r="AA3">
-        <v>0.8352482870061013</v>
+        <v>0.00770892281849328</v>
       </c>
       <c r="AB3">
-        <v>0.0549844564107971</v>
-      </c>
-      <c r="AC3">
-        <v>0.7802638305953042</v>
+        <v>0.08620308001750566</v>
       </c>
       <c r="AD3">
-        <v>6.32</v>
+        <v>55.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.32</v>
+        <v>55.3</v>
       </c>
       <c r="AG3">
-        <v>-9431.68</v>
+        <v>-10651.2</v>
       </c>
       <c r="AH3">
-        <v>0.0008925772036912022</v>
+        <v>0.008396981338354313</v>
       </c>
       <c r="AI3">
-        <v>0.0008669386366566896</v>
+        <v>0.008032653535529602</v>
       </c>
       <c r="AJ3">
-        <v>4.000916271453902</v>
+        <v>2.584740827023878</v>
       </c>
       <c r="AK3">
-        <v>4.390953360832037</v>
+        <v>2.786740273671542</v>
       </c>
       <c r="AL3">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>6.91</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.004749736960769579</v>
-      </c>
-      <c r="AO3">
-        <v>185.4269175108538</v>
+        <v>0.04115195713647864</v>
       </c>
       <c r="AP3">
-        <v>-7.088290996542914</v>
-      </c>
-      <c r="AQ3">
-        <v>185.4269175108538</v>
+        <v>-7.926179490995684</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/singapore/singapore_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_insurance_life.xlsx
@@ -587,41 +587,47 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.0259</v>
+      </c>
+      <c r="E2">
+        <v>-0.0203</v>
+      </c>
       <c r="G2">
-        <v>0.1850373264626216</v>
+        <v>0.06220427475934084</v>
       </c>
       <c r="H2">
-        <v>0.1850373264626216</v>
+        <v>0.06220427475934084</v>
       </c>
       <c r="I2">
-        <v>0.1246260275394735</v>
+        <v>0.07776554087126775</v>
       </c>
       <c r="J2">
-        <v>0.06231301376973677</v>
+        <v>0.07776554087126775</v>
       </c>
       <c r="K2">
-        <v>680</v>
+        <v>736.9</v>
       </c>
       <c r="L2">
-        <v>0.06417697745311778</v>
+        <v>0.07514480339370207</v>
       </c>
       <c r="M2">
-        <v>221.1</v>
+        <v>227.3</v>
       </c>
       <c r="N2">
-        <v>0.03385703785373025</v>
+        <v>0.03601533781214349</v>
       </c>
       <c r="O2">
-        <v>0.3251470588235294</v>
+        <v>0.308454335730764</v>
       </c>
       <c r="P2">
-        <v>221.1</v>
+        <v>227.3</v>
       </c>
       <c r="Q2">
-        <v>0.03385703785373025</v>
+        <v>0.03601533781214349</v>
       </c>
       <c r="R2">
-        <v>0.3251470588235294</v>
+        <v>0.308454335730764</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,46 +636,46 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10706.5</v>
+        <v>6660.8</v>
       </c>
       <c r="V2">
-        <v>1.639486095798113</v>
+        <v>1.055393586005831</v>
       </c>
       <c r="W2">
-        <v>0.09430952942318627</v>
+        <v>0.1090217777251746</v>
       </c>
       <c r="X2">
-        <v>0.08660060660469299</v>
+        <v>0.07484598500895731</v>
       </c>
       <c r="Y2">
-        <v>0.00770892281849328</v>
+        <v>0.03417579271621726</v>
       </c>
       <c r="AB2">
-        <v>0.08620308001750566</v>
+        <v>0.07454862032688296</v>
       </c>
       <c r="AD2">
-        <v>55.3</v>
+        <v>50.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>55.3</v>
+        <v>50.5</v>
       </c>
       <c r="AG2">
-        <v>-10651.2</v>
+        <v>-6610.3</v>
       </c>
       <c r="AH2">
-        <v>0.008396981338354313</v>
+        <v>0.007938129745193895</v>
       </c>
       <c r="AI2">
-        <v>0.008032653535529602</v>
+        <v>0.00917731295545823</v>
       </c>
       <c r="AJ2">
-        <v>2.584740827023878</v>
+        <v>22.10063523905046</v>
       </c>
       <c r="AK2">
-        <v>2.786740273671542</v>
+        <v>5.707883602452291</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -678,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.04115195713647864</v>
+        <v>0.06387553756640527</v>
       </c>
       <c r="AP2">
-        <v>-7.926179490995684</v>
+        <v>-8.361118138122945</v>
       </c>
     </row>
     <row r="3">
@@ -700,41 +706,47 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.0259</v>
+      </c>
+      <c r="E3">
+        <v>-0.0203</v>
+      </c>
       <c r="G3">
-        <v>0.1850373264626216</v>
+        <v>0.06220427475934084</v>
       </c>
       <c r="H3">
-        <v>0.1850373264626216</v>
+        <v>0.06220427475934084</v>
       </c>
       <c r="I3">
-        <v>0.1246260275394735</v>
+        <v>0.07776554087126775</v>
       </c>
       <c r="J3">
-        <v>0.06231301376973677</v>
+        <v>0.07776554087126775</v>
       </c>
       <c r="K3">
-        <v>680</v>
+        <v>736.9</v>
       </c>
       <c r="L3">
-        <v>0.06417697745311778</v>
+        <v>0.07514480339370207</v>
       </c>
       <c r="M3">
-        <v>221.1</v>
+        <v>227.3</v>
       </c>
       <c r="N3">
-        <v>0.03385703785373025</v>
+        <v>0.03601533781214349</v>
       </c>
       <c r="O3">
-        <v>0.3251470588235294</v>
+        <v>0.308454335730764</v>
       </c>
       <c r="P3">
-        <v>221.1</v>
+        <v>227.3</v>
       </c>
       <c r="Q3">
-        <v>0.03385703785373025</v>
+        <v>0.03601533781214349</v>
       </c>
       <c r="R3">
-        <v>0.3251470588235294</v>
+        <v>0.308454335730764</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -743,46 +755,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>10706.5</v>
+        <v>6660.8</v>
       </c>
       <c r="V3">
-        <v>1.639486095798113</v>
+        <v>1.055393586005831</v>
       </c>
       <c r="W3">
-        <v>0.09430952942318627</v>
+        <v>0.1090217777251746</v>
       </c>
       <c r="X3">
-        <v>0.08660060660469299</v>
+        <v>0.07484598500895731</v>
       </c>
       <c r="Y3">
-        <v>0.00770892281849328</v>
+        <v>0.03417579271621726</v>
       </c>
       <c r="AB3">
-        <v>0.08620308001750566</v>
+        <v>0.07454862032688296</v>
       </c>
       <c r="AD3">
-        <v>55.3</v>
+        <v>50.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>55.3</v>
+        <v>50.5</v>
       </c>
       <c r="AG3">
-        <v>-10651.2</v>
+        <v>-6610.3</v>
       </c>
       <c r="AH3">
-        <v>0.008396981338354313</v>
+        <v>0.007938129745193895</v>
       </c>
       <c r="AI3">
-        <v>0.008032653535529602</v>
+        <v>0.00917731295545823</v>
       </c>
       <c r="AJ3">
-        <v>2.584740827023878</v>
+        <v>22.10063523905046</v>
       </c>
       <c r="AK3">
-        <v>2.786740273671542</v>
+        <v>5.707883602452291</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -791,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.04115195713647864</v>
+        <v>0.06387553756640527</v>
       </c>
       <c r="AP3">
-        <v>-7.926179490995684</v>
+        <v>-8.361118138122945</v>
       </c>
     </row>
   </sheetData>
